--- a/VerveStacks_TUR_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_TUR_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_TUR_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12A59606-BC01-46AB-9B49-E41129CA8A1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464C8339-B387-40F2-B8BB-079D9C5B412B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="11422" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="12772" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>
@@ -1000,10 +1000,10 @@
         <v>86</v>
       </c>
       <c r="M11" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="N11" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="O11" t="s">
         <v>149</v>
@@ -1062,10 +1062,10 @@
         <v>86</v>
       </c>
       <c r="M12" t="s">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="N12" t="s">
-        <v>146</v>
+        <v>111</v>
       </c>
       <c r="O12" t="s">
         <v>149</v>
@@ -1124,10 +1124,10 @@
         <v>86</v>
       </c>
       <c r="M13" t="s">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="N13" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="O13" t="s">
         <v>149</v>
@@ -1186,10 +1186,10 @@
         <v>86</v>
       </c>
       <c r="M14" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="N14" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="O14" t="s">
         <v>149</v>
@@ -1248,10 +1248,10 @@
         <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="N15" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="O15" t="s">
         <v>149</v>
@@ -1310,10 +1310,10 @@
         <v>86</v>
       </c>
       <c r="M16" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="N16" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="O16" t="s">
         <v>149</v>
@@ -1372,10 +1372,10 @@
         <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="N17" t="s">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="O17" t="s">
         <v>149</v>
@@ -1434,10 +1434,10 @@
         <v>86</v>
       </c>
       <c r="M18" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="N18" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="O18" t="s">
         <v>149</v>
@@ -1496,10 +1496,10 @@
         <v>86</v>
       </c>
       <c r="M19" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N19" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O19" t="s">
         <v>149</v>
@@ -1558,10 +1558,10 @@
         <v>86</v>
       </c>
       <c r="M20" t="s">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="N20" t="s">
-        <v>88</v>
+        <v>138</v>
       </c>
       <c r="O20" t="s">
         <v>149</v>
@@ -1620,10 +1620,10 @@
         <v>86</v>
       </c>
       <c r="M21" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="N21" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="O21" t="s">
         <v>149</v>
@@ -1682,10 +1682,10 @@
         <v>86</v>
       </c>
       <c r="M22" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
       <c r="N22" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="O22" t="s">
         <v>149</v>
@@ -1744,10 +1744,10 @@
         <v>86</v>
       </c>
       <c r="M23" t="s">
-        <v>118</v>
+        <v>150</v>
       </c>
       <c r="N23" t="s">
-        <v>119</v>
+        <v>151</v>
       </c>
       <c r="O23" t="s">
         <v>149</v>
@@ -1806,10 +1806,10 @@
         <v>86</v>
       </c>
       <c r="M24" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="N24" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="O24" t="s">
         <v>149</v>
@@ -1868,10 +1868,10 @@
         <v>86</v>
       </c>
       <c r="M25" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="N25" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="O25" t="s">
         <v>149</v>
@@ -1930,10 +1930,10 @@
         <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="N26" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="O26" t="s">
         <v>149</v>
@@ -1992,10 +1992,10 @@
         <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="N27" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="O27" t="s">
         <v>149</v>
@@ -2030,10 +2030,10 @@
         <v>86</v>
       </c>
       <c r="M28" t="s">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="N28" t="s">
-        <v>135</v>
+        <v>105</v>
       </c>
       <c r="O28" t="s">
         <v>149</v>
@@ -2068,10 +2068,10 @@
         <v>86</v>
       </c>
       <c r="M29" t="s">
-        <v>141</v>
+        <v>90</v>
       </c>
       <c r="N29" t="s">
-        <v>142</v>
+        <v>91</v>
       </c>
       <c r="O29" t="s">
         <v>149</v>
@@ -2106,10 +2106,10 @@
         <v>86</v>
       </c>
       <c r="M30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N30" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="O30" t="s">
         <v>149</v>
@@ -2144,10 +2144,10 @@
         <v>86</v>
       </c>
       <c r="M31" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="N31" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="O31" t="s">
         <v>149</v>
@@ -2182,10 +2182,10 @@
         <v>86</v>
       </c>
       <c r="M32" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="N32" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="O32" t="s">
         <v>149</v>
@@ -2220,10 +2220,10 @@
         <v>86</v>
       </c>
       <c r="M33" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="N33" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="O33" t="s">
         <v>149</v>
@@ -2258,10 +2258,10 @@
         <v>86</v>
       </c>
       <c r="M34" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="N34" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="O34" t="s">
         <v>149</v>
@@ -2310,10 +2310,10 @@
         <v>86</v>
       </c>
       <c r="M36" t="s">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="N36" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="O36" t="s">
         <v>149</v>
@@ -2336,10 +2336,10 @@
         <v>86</v>
       </c>
       <c r="M37" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="N37" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="O37" t="s">
         <v>149</v>
@@ -2362,10 +2362,10 @@
         <v>86</v>
       </c>
       <c r="M38" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="N38" t="s">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="O38" t="s">
         <v>149</v>
@@ -2388,10 +2388,10 @@
         <v>86</v>
       </c>
       <c r="M39" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="N39" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="O39" t="s">
         <v>149</v>
@@ -2414,10 +2414,10 @@
         <v>86</v>
       </c>
       <c r="M40" t="s">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="N40" t="s">
-        <v>121</v>
+        <v>88</v>
       </c>
       <c r="O40" t="s">
         <v>149</v>
@@ -2428,10 +2428,10 @@
         <v>86</v>
       </c>
       <c r="M41" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="N41" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="O41" t="s">
         <v>149</v>
